--- a/public/templates/examples/A-005-RACIMatrixForCybersecurity-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-005-RACIMatrixForCybersecurity-EXAMPLE-L.xlsx
@@ -4,11 +4,10 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -736,7 +735,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>This matrix maps each cybersecurity function at Tri-River Regional 911 Center to the roles that carry it. The Director is accountable for governance and budget; the part-time information security analyst is accountable for day-to-day security operations; the dedicated IT team does the technical work; and the annual audit and penetration test are contracted for independence.</t>
@@ -750,14 +749,14 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Each row is a security function; each column is a role. R = Responsible (does the work); A = Accountable (owns the outcome, one per row); C = Consulted (gives input); I = Informed (kept up to date).</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>At Tri-River Regional 911 Center the Director and the information security analyst split the accountable role between governance and operations. The contracted reviewer provides the independence the audit row needs. Columns map to the Security Role Descriptions.</t>
@@ -771,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="50.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Security Function \ Role</t>
@@ -808,7 +807,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Set security &amp; privacy priorities</t>
@@ -993,7 +992,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Secure configuration &amp; patching</t>
@@ -1333,7 +1332,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="66.4" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>The annual access and control review and penetration test (row 14) are performed by a contracted independent reviewer, recorded in the IT Support Accountability Agreement. Vendors and integration partners carry the Responsible role for configuration and backup on the systems they operate. Despite the center’s size, the information security analyst is part time; the Steering Committee has flagged the role for a full-time position to deepen monitoring and detection.</t>
@@ -1347,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="34.7" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Reviewed at least annually by the information security analyst, and whenever roles, staffing, or contracts change. Last adopted May 19, 2026.</t>
@@ -1382,7 +1381,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="34.7" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1404,7 +1403,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="50.5" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1453,67 +1452,8 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>RACI Matrix: How to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Rows: each is a major cybersecurity function the center performs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Columns: each is a role. They map to the Security Role Descriptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Cells use RACI: R Responsible, A Accountable (one per row), C Consulted, I Informed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>The Director is Accountable for governance; the information security analyst is Accountable for security operations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>The annual audit and penetration test are contracted to an independent reviewer for independence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>